--- a/Data_test_sets/Test02_MissingDeadline.xlsx
+++ b/Data_test_sets/Test02_MissingDeadline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/Data_test_sets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A19DA0-E144-45C9-A93E-6BFCCADDED18}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B024F29-710B-4113-B610-9CD3B70EA876}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>Machine</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>M2</t>
-  </si>
-  <si>
-    <t>Deadline</t>
   </si>
   <si>
     <t>Order</t>
@@ -460,41 +457,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
+      <c r="D1" s="7"/>
       <c r="E1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3">
         <v>150</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="8">
         <v>18</v>
@@ -503,15 +498,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3">
         <v>200</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="8">
         <v>28</v>
@@ -520,15 +515,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3">
         <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="8">
         <v>12</v>
@@ -546,21 +541,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -568,7 +563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -584,118 +579,118 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
@@ -935,20 +930,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -971,6 +966,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A6ABA0-C4D6-4A20-974A-2B1B1E891161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -978,12 +981,4 @@
     <ds:schemaRef ds:uri="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>